--- a/서버정보/20260716_리소스배포_운영.xlsx
+++ b/서버정보/20260716_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1573E4CE-142B-4641-BD95-39235071253D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C86EACD-877A-4114-98D5-87232A9FA204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7011" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7011" uniqueCount="1057">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5502,13 +5502,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.2</t>
-  </si>
-  <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>p-com-web-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5537,6 +5530,10 @@
   </si>
   <si>
     <t>10.158.161.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6070,7 +6067,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6428,14 +6425,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6443,13 +6434,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12410,124 +12395,124 @@
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B62" s="125" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="125" t="str" cm="1">
+      <c r="B62" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="74" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D62" s="125" t="s">
+      <c r="D62" s="74" t="s">
         <v>1036</v>
       </c>
-      <c r="E62" s="125" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F62" s="125" t="str">
+      <c r="E62" s="74" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F62" s="74" t="str">
         <f t="shared" ref="F62:F65" si="18">SUBSTITUTE(E62, "hazr-", "")&amp;"-rule"&amp;O62</f>
         <v>p-com-esnweb-lb-rule8080</v>
       </c>
-      <c r="G62" s="125" t="str">
+      <c r="G62" s="74" t="str">
         <f t="shared" ref="G62:G65" si="19">SUBSTITUTE(E62, "hazr-", "")&amp;"-fe"</f>
         <v>p-com-esnweb-lb-fe</v>
       </c>
-      <c r="H62" s="125" t="s">
+      <c r="H62" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I62" s="125">
+      <c r="I62" s="74">
         <v>8080</v>
       </c>
-      <c r="J62" s="125" t="b">
+      <c r="J62" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K62" s="125" t="str">
+      <c r="K62" s="74" t="str">
         <f t="shared" ref="K62:K65" si="20">SUBSTITUTE(E62, "hazr-", "")&amp;"-bp"</f>
         <v>p-com-esnweb-lb-bp</v>
       </c>
-      <c r="L62" s="125">
+      <c r="L62" s="74">
         <v>8080</v>
       </c>
-      <c r="M62" s="125" t="str">
+      <c r="M62" s="74" t="str">
         <f t="shared" ref="M62:M65" si="21">SUBSTITUTE(E62, "hazr-", "")&amp;"-pb"&amp;IF(O62="", "", O62)</f>
         <v>p-com-esnweb-lb-pb8080</v>
       </c>
-      <c r="N62" s="125" t="s">
+      <c r="N62" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="O62" s="125">
+      <c r="O62" s="74">
         <v>8080</v>
       </c>
-      <c r="P62" s="125">
+      <c r="P62" s="74">
         <v>4</v>
       </c>
-      <c r="Q62" s="125" t="s">
+      <c r="Q62" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="R62" s="125" t="b">
-        <v>1</v>
-      </c>
-      <c r="S62" s="125" t="b">
+      <c r="R62" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="S62" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="125" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="125" t="str" cm="1">
+      <c r="B63" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="74" t="str" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D63" s="125" t="s">
+      <c r="D63" s="74" t="s">
         <v>1036</v>
       </c>
-      <c r="E63" s="125" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F63" s="125" t="str">
+      <c r="E63" s="74" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F63" s="74" t="str">
         <f t="shared" si="18"/>
         <v>p-com-esnweb-lb-rule443</v>
       </c>
-      <c r="G63" s="125" t="str">
+      <c r="G63" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-com-esnweb-lb-fe</v>
       </c>
-      <c r="H63" s="125" t="s">
+      <c r="H63" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I63" s="125">
+      <c r="I63" s="74">
         <v>443</v>
       </c>
-      <c r="J63" s="125" t="b">
+      <c r="J63" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="K63" s="125" t="str">
+      <c r="K63" s="74" t="str">
         <f t="shared" si="20"/>
         <v>p-com-esnweb-lb-bp</v>
       </c>
-      <c r="L63" s="125">
+      <c r="L63" s="74">
         <v>443</v>
       </c>
-      <c r="M63" s="125" t="str">
+      <c r="M63" s="74" t="str">
         <f t="shared" si="21"/>
         <v>p-com-esnweb-lb-pb443</v>
       </c>
-      <c r="N63" s="125" t="s">
+      <c r="N63" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="O63" s="125">
+      <c r="O63" s="74">
         <v>443</v>
       </c>
-      <c r="P63" s="125">
+      <c r="P63" s="74">
         <v>4</v>
       </c>
-      <c r="Q63" s="125" t="s">
+      <c r="Q63" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="R63" s="125" t="b">
-        <v>1</v>
-      </c>
-      <c r="S63" s="125" t="b">
+      <c r="R63" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="S63" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12543,7 +12528,7 @@
         <v>1036</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F64" s="82" t="str">
         <f t="shared" si="18"/>
@@ -12604,7 +12589,7 @@
         <v>1036</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F65" s="82" t="str">
         <f t="shared" si="18"/>
@@ -24347,7 +24332,7 @@
         <v>986</v>
       </c>
       <c r="O129" s="115" t="str">
-        <f>SUBSTITUTE(F129,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="O129:O135" si="12">SUBSTITUTE(F129,"hazr-","")&amp;"-osdisk"</f>
         <v>p-dtg-bbigeoap01-osdisk</v>
       </c>
       <c r="P129" s="116">
@@ -24360,7 +24345,7 @@
       <c r="S129" s="95"/>
       <c r="T129" s="95"/>
       <c r="U129" s="95" t="str">
-        <f>SUBSTITUTE(F129,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U129:U135" si="13">SUBSTITUTE(F129,"hazr-","")&amp;"-nic"</f>
         <v>p-dtg-bbigeoap01-nic</v>
       </c>
       <c r="V129" s="95" t="b">
@@ -24436,7 +24421,7 @@
         <v>986</v>
       </c>
       <c r="O130" s="113" t="str">
-        <f>SUBSTITUTE(F130,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="12"/>
         <v>p-dtg-bbigeoap02-osdisk</v>
       </c>
       <c r="P130" s="80">
@@ -24449,7 +24434,7 @@
       <c r="S130" s="74"/>
       <c r="T130" s="74"/>
       <c r="U130" s="74" t="str">
-        <f>SUBSTITUTE(F130,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="13"/>
         <v>p-dtg-bbigeoap02-nic</v>
       </c>
       <c r="V130" s="74" t="b">
@@ -24524,7 +24509,7 @@
         <v>1034</v>
       </c>
       <c r="O131" s="115" t="str">
-        <f>SUBSTITUTE(F131,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="12"/>
         <v>p-if-hipsap01-osdisk</v>
       </c>
       <c r="P131" s="116">
@@ -24537,7 +24522,7 @@
       <c r="S131" s="95"/>
       <c r="T131" s="95"/>
       <c r="U131" s="95" t="str">
-        <f>SUBSTITUTE(F131,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="13"/>
         <v>p-if-hipsap01-nic</v>
       </c>
       <c r="V131" s="95" t="b">
@@ -24574,11 +24559,11 @@
       <c r="B132" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C132" s="119" t="str" cm="1">
+      <c r="C132" s="95" t="str" cm="1">
         <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($F132, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D132" s="119" t="s">
+      <c r="D132" s="95" t="s">
         <v>1036</v>
       </c>
       <c r="E132" s="95" t="s">
@@ -24608,11 +24593,11 @@
       <c r="M132" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N132" s="120" t="s">
-        <v>1049</v>
-      </c>
-      <c r="O132" s="121" t="str">
-        <f>SUBSTITUTE(F132,"hazr-","")&amp;"-osdisk"</f>
+      <c r="N132" s="119" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O132" s="115" t="str">
+        <f t="shared" si="12"/>
         <v>p-com-esnweb01-osdisk</v>
       </c>
       <c r="P132" s="80">
@@ -24621,11 +24606,11 @@
       <c r="Q132" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="R132" s="119"/>
+      <c r="R132" s="95"/>
       <c r="S132" s="95"/>
-      <c r="T132" s="119"/>
-      <c r="U132" s="119" t="str">
-        <f>SUBSTITUTE(F132,"hazr-","")&amp;"-nic"</f>
+      <c r="T132" s="95"/>
+      <c r="U132" s="95" t="str">
+        <f t="shared" si="13"/>
         <v>p-com-esnweb01-nic</v>
       </c>
       <c r="V132" s="95" t="b">
@@ -24641,7 +24626,7 @@
         <v>345</v>
       </c>
       <c r="Z132" s="74" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AA132" s="74" t="b">
         <v>1</v>
@@ -24662,11 +24647,11 @@
       <c r="B133" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C133" s="119" t="str" cm="1">
+      <c r="C133" s="95" t="str" cm="1">
         <f t="array" ref="C133">UPPER(INDEX(_xlfn.TEXTSPLIT($F133, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D133" s="119" t="s">
+      <c r="D133" s="95" t="s">
         <v>1036</v>
       </c>
       <c r="E133" s="95" t="s">
@@ -24696,11 +24681,11 @@
       <c r="M133" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N133" s="120" t="s">
-        <v>1049</v>
-      </c>
-      <c r="O133" s="121" t="str">
-        <f>SUBSTITUTE(F133,"hazr-","")&amp;"-osdisk"</f>
+      <c r="N133" s="119" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O133" s="115" t="str">
+        <f t="shared" si="12"/>
         <v>p-com-esnweb02-osdisk</v>
       </c>
       <c r="P133" s="80">
@@ -24709,11 +24694,11 @@
       <c r="Q133" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="R133" s="119"/>
+      <c r="R133" s="95"/>
       <c r="S133" s="95"/>
-      <c r="T133" s="119"/>
-      <c r="U133" s="119" t="str">
-        <f>SUBSTITUTE(F133,"hazr-","")&amp;"-nic"</f>
+      <c r="T133" s="95"/>
+      <c r="U133" s="95" t="str">
+        <f t="shared" si="13"/>
         <v>p-com-esnweb02-nic</v>
       </c>
       <c r="V133" s="95" t="b">
@@ -24729,7 +24714,7 @@
         <v>345</v>
       </c>
       <c r="Z133" s="74" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AA133" s="95" t="b">
         <v>1</v>
@@ -24750,11 +24735,11 @@
       <c r="B134" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C134" s="119" t="str" cm="1">
+      <c r="C134" s="95" t="str" cm="1">
         <f t="array" ref="C134">UPPER(INDEX(_xlfn.TEXTSPLIT($F134, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D134" s="119" t="s">
+      <c r="D134" s="95" t="s">
         <v>1036</v>
       </c>
       <c r="E134" s="95" t="s">
@@ -24784,11 +24769,11 @@
       <c r="M134" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N134" s="120" t="s">
-        <v>1048</v>
-      </c>
-      <c r="O134" s="121" t="str">
-        <f>SUBSTITUTE(F134,"hazr-","")&amp;"-osdisk"</f>
+      <c r="N134" s="119" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O134" s="115" t="str">
+        <f t="shared" si="12"/>
         <v>p-com-esnap01-osdisk</v>
       </c>
       <c r="P134" s="116">
@@ -24797,11 +24782,11 @@
       <c r="Q134" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="R134" s="119"/>
+      <c r="R134" s="95"/>
       <c r="S134" s="95"/>
-      <c r="T134" s="119"/>
-      <c r="U134" s="119" t="str">
-        <f>SUBSTITUTE(F134,"hazr-","")&amp;"-nic"</f>
+      <c r="T134" s="95"/>
+      <c r="U134" s="95" t="str">
+        <f t="shared" si="13"/>
         <v>p-com-esnap01-nic</v>
       </c>
       <c r="V134" s="95" t="b">
@@ -24817,7 +24802,7 @@
         <v>338</v>
       </c>
       <c r="Z134" s="74" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="AA134" s="74" t="b">
         <v>1</v>
@@ -24838,11 +24823,11 @@
       <c r="B135" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="119" t="str" cm="1">
+      <c r="C135" s="95" t="str" cm="1">
         <f t="array" ref="C135">UPPER(INDEX(_xlfn.TEXTSPLIT($F135, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D135" s="119" t="s">
+      <c r="D135" s="95" t="s">
         <v>1036</v>
       </c>
       <c r="E135" s="95" t="s">
@@ -24872,11 +24857,11 @@
       <c r="M135" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N135" s="120" t="s">
-        <v>1048</v>
-      </c>
-      <c r="O135" s="121" t="str">
-        <f>SUBSTITUTE(F135,"hazr-","")&amp;"-osdisk"</f>
+      <c r="N135" s="119" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O135" s="115" t="str">
+        <f t="shared" si="12"/>
         <v>p-com-esnap02-osdisk</v>
       </c>
       <c r="P135" s="80">
@@ -24885,11 +24870,11 @@
       <c r="Q135" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="R135" s="119"/>
+      <c r="R135" s="95"/>
       <c r="S135" s="95"/>
-      <c r="T135" s="119"/>
-      <c r="U135" s="119" t="str">
-        <f>SUBSTITUTE(F135,"hazr-","")&amp;"-nic"</f>
+      <c r="T135" s="95"/>
+      <c r="U135" s="95" t="str">
+        <f t="shared" si="13"/>
         <v>p-com-esnap02-nic</v>
       </c>
       <c r="V135" s="95" t="b">
@@ -24905,7 +24890,7 @@
         <v>338</v>
       </c>
       <c r="Z135" s="74" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="AA135" s="95" t="b">
         <v>1</v>
@@ -38684,7 +38669,7 @@
         <f t="array" ref="C150">UPPER(INDEX(_xlfn.TEXTSPLIT($E150, "-"), 2))</f>
         <v>COM</v>
       </c>
-      <c r="D150" s="122" t="s">
+      <c r="D150" s="120" t="s">
         <v>317</v>
       </c>
       <c r="E150" s="73" t="str">
@@ -38694,26 +38679,26 @@
       <c r="F150" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="G150" s="122" t="s">
+      <c r="G150" s="120" t="s">
         <v>345</v>
       </c>
-      <c r="H150" s="122" t="s">
-        <v>1050</v>
-      </c>
-      <c r="I150" s="122" t="s">
+      <c r="H150" s="120" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I150" s="120" t="s">
         <v>1037</v>
       </c>
-      <c r="J150" s="122" t="s">
+      <c r="J150" s="120" t="s">
         <v>1036</v>
       </c>
       <c r="K150" s="73" t="str">
         <f t="shared" si="4"/>
         <v>p-com-esnweb01-nic</v>
       </c>
-      <c r="L150" s="122" t="s">
+      <c r="L150" s="120" t="s">
         <v>226</v>
       </c>
-      <c r="M150" s="122"/>
+      <c r="M150" s="120"/>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B151" s="80" t="s">
@@ -38722,7 +38707,7 @@
       <c r="C151" s="80" t="s">
         <v>1030</v>
       </c>
-      <c r="D151" s="123" t="s">
+      <c r="D151" s="121" t="s">
         <v>317</v>
       </c>
       <c r="E151" s="74" t="str">
@@ -38732,26 +38717,26 @@
       <c r="F151" s="74" t="s">
         <v>317</v>
       </c>
-      <c r="G151" s="123" t="s">
+      <c r="G151" s="121" t="s">
         <v>345</v>
       </c>
-      <c r="H151" s="124" t="s">
+      <c r="H151" s="121" t="s">
         <v>240</v>
       </c>
-      <c r="I151" s="123" t="s">
+      <c r="I151" s="121" t="s">
         <v>1038</v>
       </c>
-      <c r="J151" s="123" t="s">
+      <c r="J151" s="121" t="s">
         <v>1036</v>
       </c>
       <c r="K151" s="74" t="str">
         <f t="shared" si="4"/>
         <v>p-com-esnweb02-nic</v>
       </c>
-      <c r="L151" s="123" t="s">
+      <c r="L151" s="121" t="s">
         <v>226</v>
       </c>
-      <c r="M151" s="123"/>
+      <c r="M151" s="121"/>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B152" s="78" t="s">
@@ -38761,7 +38746,7 @@
         <f t="array" ref="C152">UPPER(INDEX(_xlfn.TEXTSPLIT($E152, "-"), 2))</f>
         <v>COM</v>
       </c>
-      <c r="D152" s="122" t="s">
+      <c r="D152" s="120" t="s">
         <v>317</v>
       </c>
       <c r="E152" s="73" t="str">
@@ -38771,26 +38756,26 @@
       <c r="F152" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="G152" s="122" t="s">
+      <c r="G152" s="120" t="s">
         <v>338</v>
       </c>
-      <c r="H152" s="122" t="s">
-        <v>1051</v>
-      </c>
-      <c r="I152" s="122" t="s">
+      <c r="H152" s="120" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I152" s="120" t="s">
         <v>1039</v>
       </c>
-      <c r="J152" s="122" t="s">
+      <c r="J152" s="120" t="s">
         <v>1036</v>
       </c>
       <c r="K152" s="73" t="str">
         <f t="shared" si="4"/>
         <v>p-com-esnap01-nic</v>
       </c>
-      <c r="L152" s="122" t="s">
+      <c r="L152" s="120" t="s">
         <v>226</v>
       </c>
-      <c r="M152" s="122"/>
+      <c r="M152" s="120"/>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B153" s="80" t="s">
@@ -38799,7 +38784,7 @@
       <c r="C153" s="80" t="s">
         <v>1030</v>
       </c>
-      <c r="D153" s="123" t="s">
+      <c r="D153" s="121" t="s">
         <v>317</v>
       </c>
       <c r="E153" s="74" t="str">
@@ -38809,26 +38794,26 @@
       <c r="F153" s="74" t="s">
         <v>317</v>
       </c>
-      <c r="G153" s="123" t="s">
+      <c r="G153" s="121" t="s">
         <v>338</v>
       </c>
-      <c r="H153" s="124" t="s">
-        <v>1051</v>
-      </c>
-      <c r="I153" s="123" t="s">
+      <c r="H153" s="121" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I153" s="121" t="s">
         <v>1040</v>
       </c>
-      <c r="J153" s="123" t="s">
+      <c r="J153" s="121" t="s">
         <v>1036</v>
       </c>
       <c r="K153" s="74" t="str">
         <f t="shared" si="4"/>
         <v>p-com-esnap02-nic</v>
       </c>
-      <c r="L153" s="123" t="s">
+      <c r="L153" s="121" t="s">
         <v>226</v>
       </c>
-      <c r="M153" s="123"/>
+      <c r="M153" s="121"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:M146" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}"/>
@@ -43457,26 +43442,26 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="125" t="s">
+      <c r="B41" s="74" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="74" t="str" cm="1">
         <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($F41, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D41" s="125" t="s">
+      <c r="D41" s="74" t="s">
         <v>1036</v>
       </c>
-      <c r="E41" s="125" t="s">
+      <c r="E41" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="125" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G41" s="125" t="s">
+      <c r="F41" s="74" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G41" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="H41" s="125" t="s">
+      <c r="H41" s="74" t="s">
         <v>1016</v>
       </c>
       <c r="I41" s="74" t="s">
@@ -43485,26 +43470,26 @@
       <c r="J41" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="K41" s="125" t="str">
+      <c r="K41" s="74" t="str">
         <f t="shared" si="4"/>
         <v>p-com-esnweb-lb-fe</v>
       </c>
-      <c r="L41" s="125" t="s">
-        <v>317</v>
-      </c>
-      <c r="M41" s="125" t="s">
+      <c r="L41" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="M41" s="74" t="s">
         <v>345</v>
       </c>
-      <c r="N41" s="125" t="s">
-        <v>1050</v>
-      </c>
-      <c r="O41" s="125" t="s">
+      <c r="N41" s="74" t="s">
+        <v>1048</v>
+      </c>
+      <c r="O41" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P41" s="125" t="s">
-        <v>1056</v>
-      </c>
-      <c r="Q41" s="125" t="str">
+      <c r="P41" s="74" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Q41" s="74" t="str">
         <f t="shared" si="1"/>
         <v>p-com-esnweb-lb-bp</v>
       </c>
@@ -43524,7 +43509,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="82" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G42" s="82" t="s">
         <v>111</v>
@@ -43549,13 +43534,13 @@
         <v>338</v>
       </c>
       <c r="N42" s="82" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="O42" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P42" s="82" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="Q42" s="82" t="str">
         <f t="shared" si="1"/>
@@ -45582,66 +45567,66 @@
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B62" s="125" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="125" t="str" cm="1">
+      <c r="B62" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="74" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D62" s="125" t="s">
+      <c r="D62" s="74" t="s">
         <v>1036</v>
       </c>
-      <c r="E62" s="125" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F62" s="126" t="str">
+      <c r="E62" s="74" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F62" s="122" t="str">
         <f t="shared" ref="F62:F65" si="14">SUBSTITUTE(E62, "hazr-", "")&amp;"-pb"&amp;H62</f>
         <v>p-com-esnweb-lb-pb8080</v>
       </c>
-      <c r="G62" s="125" t="s">
+      <c r="G62" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H62" s="125">
+      <c r="H62" s="74">
         <v>8080</v>
       </c>
-      <c r="I62" s="125"/>
-      <c r="J62" s="125">
+      <c r="I62" s="74"/>
+      <c r="J62" s="74">
         <v>5</v>
       </c>
-      <c r="K62" s="125">
+      <c r="K62" s="74">
         <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B63" s="125" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="125" t="str" cm="1">
+      <c r="B63" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="74" t="str" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D63" s="125" t="s">
+      <c r="D63" s="74" t="s">
         <v>1036</v>
       </c>
-      <c r="E63" s="125" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F63" s="126" t="str">
+      <c r="E63" s="74" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F63" s="122" t="str">
         <f t="shared" si="14"/>
         <v>p-com-esnweb-lb-pb443</v>
       </c>
-      <c r="G63" s="125" t="s">
+      <c r="G63" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H63" s="125">
+      <c r="H63" s="74">
         <v>443</v>
       </c>
-      <c r="I63" s="125"/>
-      <c r="J63" s="125">
+      <c r="I63" s="74"/>
+      <c r="J63" s="74">
         <v>5</v>
       </c>
-      <c r="K63" s="125">
+      <c r="K63" s="74">
         <v>2</v>
       </c>
     </row>
@@ -45657,7 +45642,7 @@
         <v>1036</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F64" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45689,7 +45674,7 @@
         <v>1036</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F65" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45716,9 +45701,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45866,26 +45854,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -45909,9 +45886,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260716_리소스배포_운영.xlsx
+++ b/서버정보/20260716_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C86EACD-877A-4114-98D5-87232A9FA204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05914490-5BA1-4464-B4C2-9551C68F8E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7011" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7008" uniqueCount="1056">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5448,10 +5448,6 @@
   </si>
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -12403,10 +12399,10 @@
         <v>COM</v>
       </c>
       <c r="D62" s="74" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E62" s="74" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F62" s="74" t="str">
         <f t="shared" ref="F62:F65" si="18">SUBSTITUTE(E62, "hazr-", "")&amp;"-rule"&amp;O62</f>
@@ -12464,10 +12460,10 @@
         <v>COM</v>
       </c>
       <c r="D63" s="74" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F63" s="74" t="str">
         <f t="shared" si="18"/>
@@ -12525,10 +12521,10 @@
         <v>COM</v>
       </c>
       <c r="D64" s="82" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F64" s="82" t="str">
         <f t="shared" si="18"/>
@@ -12586,10 +12582,10 @@
         <v>COM</v>
       </c>
       <c r="D65" s="82" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F65" s="82" t="str">
         <f t="shared" si="18"/>
@@ -24564,19 +24560,19 @@
         <v>COM</v>
       </c>
       <c r="D132" s="95" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E132" s="95" t="s">
         <v>24</v>
       </c>
       <c r="F132" s="95" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G132" s="95" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H132" s="95" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I132" s="95">
         <v>16</v>
@@ -24594,7 +24590,7 @@
         <v>992</v>
       </c>
       <c r="N132" s="119" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="O132" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24626,7 +24622,7 @@
         <v>345</v>
       </c>
       <c r="Z132" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AA132" s="74" t="b">
         <v>1</v>
@@ -24652,16 +24648,16 @@
         <v>COM</v>
       </c>
       <c r="D133" s="95" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E133" s="95" t="s">
         <v>24</v>
       </c>
       <c r="F133" s="95" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G133" s="95" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H133" s="95" t="s">
         <v>596</v>
@@ -24682,7 +24678,7 @@
         <v>992</v>
       </c>
       <c r="N133" s="119" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="O133" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24714,7 +24710,7 @@
         <v>345</v>
       </c>
       <c r="Z133" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AA133" s="95" t="b">
         <v>1</v>
@@ -24740,19 +24736,19 @@
         <v>COM</v>
       </c>
       <c r="D134" s="95" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E134" s="95" t="s">
         <v>24</v>
       </c>
       <c r="F134" s="95" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G134" s="95" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H134" s="95" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I134" s="95">
         <v>32</v>
@@ -24770,7 +24766,7 @@
         <v>992</v>
       </c>
       <c r="N134" s="119" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="O134" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24802,7 +24798,7 @@
         <v>338</v>
       </c>
       <c r="Z134" s="74" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="AA134" s="74" t="b">
         <v>1</v>
@@ -24828,19 +24824,19 @@
         <v>COM</v>
       </c>
       <c r="D135" s="95" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E135" s="95" t="s">
         <v>24</v>
       </c>
       <c r="F135" s="95" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G135" s="95" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H135" s="95" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I135" s="95">
         <v>32</v>
@@ -24858,7 +24854,7 @@
         <v>992</v>
       </c>
       <c r="N135" s="119" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="O135" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24890,7 +24886,7 @@
         <v>338</v>
       </c>
       <c r="Z135" s="74" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="AA135" s="95" t="b">
         <v>1</v>
@@ -32602,13 +32598,13 @@
         <v>COM</v>
       </c>
       <c r="D145" s="78" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E145" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F145" s="78" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G145" s="73" t="str">
         <f t="shared" ref="G145:G148" si="0">SUBSTITUTE(F145,"hazr-","")&amp;"-disk01"</f>
@@ -32656,13 +32652,13 @@
         <v>COM</v>
       </c>
       <c r="D146" s="80" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E146" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F146" s="80" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G146" s="74" t="str">
         <f t="shared" si="0"/>
@@ -32710,13 +32706,13 @@
         <v>COM</v>
       </c>
       <c r="D147" s="78" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E147" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F147" s="78" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G147" s="73" t="str">
         <f t="shared" si="0"/>
@@ -32764,13 +32760,13 @@
         <v>COM</v>
       </c>
       <c r="D148" s="80" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E148" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F148" s="80" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G148" s="74" t="str">
         <f t="shared" si="0"/>
@@ -38627,8 +38623,9 @@
       <c r="B149" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="C149" s="80" t="s">
-        <v>1035</v>
+      <c r="C149" s="74" t="str" cm="1">
+        <f t="array" ref="C149">UPPER(INDEX(_xlfn.TEXTSPLIT($E149, "-"), 2))</f>
+        <v>IF</v>
       </c>
       <c r="D149" s="74" t="s">
         <v>317</v>
@@ -38665,7 +38662,7 @@
       <c r="B150" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C150" s="78" t="str" cm="1">
+      <c r="C150" s="120" t="str" cm="1">
         <f t="array" ref="C150">UPPER(INDEX(_xlfn.TEXTSPLIT($E150, "-"), 2))</f>
         <v>COM</v>
       </c>
@@ -38683,13 +38680,13 @@
         <v>345</v>
       </c>
       <c r="H150" s="120" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I150" s="120" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J150" s="120" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="K150" s="73" t="str">
         <f t="shared" si="4"/>
@@ -38704,8 +38701,9 @@
       <c r="B151" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="C151" s="80" t="s">
-        <v>1030</v>
+      <c r="C151" s="121" t="str" cm="1">
+        <f t="array" ref="C151">UPPER(INDEX(_xlfn.TEXTSPLIT($E151, "-"), 2))</f>
+        <v>COM</v>
       </c>
       <c r="D151" s="121" t="s">
         <v>317</v>
@@ -38724,10 +38722,10 @@
         <v>240</v>
       </c>
       <c r="I151" s="121" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="J151" s="121" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="K151" s="74" t="str">
         <f t="shared" si="4"/>
@@ -38742,7 +38740,7 @@
       <c r="B152" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C152" s="78" t="str" cm="1">
+      <c r="C152" s="120" t="str" cm="1">
         <f t="array" ref="C152">UPPER(INDEX(_xlfn.TEXTSPLIT($E152, "-"), 2))</f>
         <v>COM</v>
       </c>
@@ -38760,13 +38758,13 @@
         <v>338</v>
       </c>
       <c r="H152" s="120" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="I152" s="120" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="J152" s="120" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="K152" s="73" t="str">
         <f t="shared" si="4"/>
@@ -38781,8 +38779,9 @@
       <c r="B153" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="C153" s="80" t="s">
-        <v>1030</v>
+      <c r="C153" s="121" t="str" cm="1">
+        <f t="array" ref="C153">UPPER(INDEX(_xlfn.TEXTSPLIT($E153, "-"), 2))</f>
+        <v>COM</v>
       </c>
       <c r="D153" s="121" t="s">
         <v>317</v>
@@ -38798,13 +38797,13 @@
         <v>338</v>
       </c>
       <c r="H153" s="121" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="I153" s="121" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="J153" s="121" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="K153" s="74" t="str">
         <f t="shared" si="4"/>
@@ -43450,13 +43449,13 @@
         <v>COM</v>
       </c>
       <c r="D41" s="74" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E41" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F41" s="74" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G41" s="74" t="s">
         <v>111</v>
@@ -43481,13 +43480,13 @@
         <v>345</v>
       </c>
       <c r="N41" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="O41" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P41" s="74" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="Q41" s="74" t="str">
         <f t="shared" si="1"/>
@@ -43503,13 +43502,13 @@
         <v>COM</v>
       </c>
       <c r="D42" s="82" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E42" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F42" s="82" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G42" s="82" t="s">
         <v>111</v>
@@ -43534,13 +43533,13 @@
         <v>338</v>
       </c>
       <c r="N42" s="82" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="O42" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P42" s="82" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="Q42" s="82" t="str">
         <f t="shared" si="1"/>
@@ -45575,10 +45574,10 @@
         <v>COM</v>
       </c>
       <c r="D62" s="74" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E62" s="74" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F62" s="122" t="str">
         <f t="shared" ref="F62:F65" si="14">SUBSTITUTE(E62, "hazr-", "")&amp;"-pb"&amp;H62</f>
@@ -45607,10 +45606,10 @@
         <v>COM</v>
       </c>
       <c r="D63" s="74" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F63" s="122" t="str">
         <f t="shared" si="14"/>
@@ -45639,10 +45638,10 @@
         <v>COM</v>
       </c>
       <c r="D64" s="82" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F64" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45671,10 +45670,10 @@
         <v>COM</v>
       </c>
       <c r="D65" s="82" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F65" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45701,12 +45700,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45854,15 +45850,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -45886,17 +45893,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260716_리소스배포_운영.xlsx
+++ b/서버정보/20260716_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05914490-5BA1-4464-B4C2-9551C68F8E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC1DE4A-1685-4346-B7CD-B5A6013831AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -5479,14 +5479,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.158.161.11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.158.161.12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D16ls_v5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5525,11 +5517,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.158.161.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.162.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.162.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.162.10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12402,7 +12402,7 @@
         <v>1035</v>
       </c>
       <c r="E62" s="74" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F62" s="74" t="str">
         <f t="shared" ref="F62:F65" si="18">SUBSTITUTE(E62, "hazr-", "")&amp;"-rule"&amp;O62</f>
@@ -12463,7 +12463,7 @@
         <v>1035</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F63" s="74" t="str">
         <f t="shared" si="18"/>
@@ -12524,7 +12524,7 @@
         <v>1035</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F64" s="82" t="str">
         <f t="shared" si="18"/>
@@ -12585,7 +12585,7 @@
         <v>1035</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F65" s="82" t="str">
         <f t="shared" si="18"/>
@@ -24572,7 +24572,7 @@
         <v>1040</v>
       </c>
       <c r="H132" s="95" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="I132" s="95">
         <v>16</v>
@@ -24590,7 +24590,7 @@
         <v>992</v>
       </c>
       <c r="N132" s="119" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="O132" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24622,7 +24622,7 @@
         <v>345</v>
       </c>
       <c r="Z132" s="74" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AA132" s="74" t="b">
         <v>1</v>
@@ -24678,7 +24678,7 @@
         <v>992</v>
       </c>
       <c r="N133" s="119" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="O133" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24710,7 +24710,7 @@
         <v>345</v>
       </c>
       <c r="Z133" s="74" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AA133" s="95" t="b">
         <v>1</v>
@@ -24745,10 +24745,10 @@
         <v>1038</v>
       </c>
       <c r="G134" s="95" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="H134" s="95" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="I134" s="95">
         <v>32</v>
@@ -24766,7 +24766,7 @@
         <v>992</v>
       </c>
       <c r="N134" s="119" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="O134" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24798,7 +24798,7 @@
         <v>338</v>
       </c>
       <c r="Z134" s="74" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="AA134" s="74" t="b">
         <v>1</v>
@@ -24833,10 +24833,10 @@
         <v>1039</v>
       </c>
       <c r="G135" s="95" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H135" s="95" t="s">
         <v>1043</v>
-      </c>
-      <c r="H135" s="95" t="s">
-        <v>1045</v>
       </c>
       <c r="I135" s="95">
         <v>32</v>
@@ -24854,7 +24854,7 @@
         <v>992</v>
       </c>
       <c r="N135" s="119" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="O135" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24886,7 +24886,7 @@
         <v>338</v>
       </c>
       <c r="Z135" s="74" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="AA135" s="95" t="b">
         <v>1</v>
@@ -38680,7 +38680,7 @@
         <v>345</v>
       </c>
       <c r="H150" s="120" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="I150" s="120" t="s">
         <v>1036</v>
@@ -38758,7 +38758,7 @@
         <v>338</v>
       </c>
       <c r="H152" s="120" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="I152" s="120" t="s">
         <v>1038</v>
@@ -38797,7 +38797,7 @@
         <v>338</v>
       </c>
       <c r="H153" s="121" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="I153" s="121" t="s">
         <v>1039</v>
@@ -43455,7 +43455,7 @@
         <v>24</v>
       </c>
       <c r="F41" s="74" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="G41" s="74" t="s">
         <v>111</v>
@@ -43480,13 +43480,13 @@
         <v>345</v>
       </c>
       <c r="N41" s="74" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="O41" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P41" s="74" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="Q41" s="74" t="str">
         <f t="shared" si="1"/>
@@ -43508,7 +43508,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="82" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G42" s="82" t="s">
         <v>111</v>
@@ -43533,13 +43533,13 @@
         <v>338</v>
       </c>
       <c r="N42" s="82" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="O42" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P42" s="82" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="Q42" s="82" t="str">
         <f t="shared" si="1"/>
@@ -45577,7 +45577,7 @@
         <v>1035</v>
       </c>
       <c r="E62" s="74" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F62" s="122" t="str">
         <f t="shared" ref="F62:F65" si="14">SUBSTITUTE(E62, "hazr-", "")&amp;"-pb"&amp;H62</f>
@@ -45609,7 +45609,7 @@
         <v>1035</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F63" s="122" t="str">
         <f t="shared" si="14"/>
@@ -45641,7 +45641,7 @@
         <v>1035</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F64" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45673,7 +45673,7 @@
         <v>1035</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F65" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45700,9 +45700,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45850,26 +45853,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -45893,9 +45885,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260716_리소스배포_운영.xlsx
+++ b/서버정보/20260716_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC1DE4A-1685-4346-B7CD-B5A6013831AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871FBA07-D810-4FB4-9D7F-D6E44C70DAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7008" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7008" uniqueCount="1055">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5494,13 +5494,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>p-com-ap-sn</t>
-  </si>
-  <si>
-    <t>p-com-ap-sn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-p-com-esnweb-lb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5530,6 +5523,10 @@
   </si>
   <si>
     <t>10.158.162.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p-com-ap-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12402,7 +12399,7 @@
         <v>1035</v>
       </c>
       <c r="E62" s="74" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F62" s="74" t="str">
         <f t="shared" ref="F62:F65" si="18">SUBSTITUTE(E62, "hazr-", "")&amp;"-rule"&amp;O62</f>
@@ -12463,7 +12460,7 @@
         <v>1035</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F63" s="74" t="str">
         <f t="shared" si="18"/>
@@ -12524,7 +12521,7 @@
         <v>1035</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F64" s="82" t="str">
         <f t="shared" si="18"/>
@@ -12585,7 +12582,7 @@
         <v>1035</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F65" s="82" t="str">
         <f t="shared" si="18"/>
@@ -24590,7 +24587,7 @@
         <v>992</v>
       </c>
       <c r="N132" s="119" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="O132" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24678,7 +24675,7 @@
         <v>992</v>
       </c>
       <c r="N133" s="119" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="O133" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24745,7 +24742,7 @@
         <v>1038</v>
       </c>
       <c r="G134" s="95" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="H134" s="95" t="s">
         <v>1044</v>
@@ -24766,7 +24763,7 @@
         <v>992</v>
       </c>
       <c r="N134" s="119" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="O134" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24798,7 +24795,7 @@
         <v>338</v>
       </c>
       <c r="Z134" s="74" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AA134" s="74" t="b">
         <v>1</v>
@@ -24833,7 +24830,7 @@
         <v>1039</v>
       </c>
       <c r="G135" s="95" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H135" s="95" t="s">
         <v>1043</v>
@@ -24854,7 +24851,7 @@
         <v>992</v>
       </c>
       <c r="N135" s="119" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="O135" s="115" t="str">
         <f t="shared" si="12"/>
@@ -24886,7 +24883,7 @@
         <v>338</v>
       </c>
       <c r="Z135" s="74" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AA135" s="95" t="b">
         <v>1</v>
@@ -32536,6 +32533,7 @@
       <c r="R143" s="73"/>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A144" s="99"/>
       <c r="B144" s="74" t="s">
         <v>23</v>
       </c>
@@ -38758,7 +38756,7 @@
         <v>338</v>
       </c>
       <c r="H152" s="120" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="I152" s="120" t="s">
         <v>1038</v>
@@ -38797,7 +38795,7 @@
         <v>338</v>
       </c>
       <c r="H153" s="121" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="I153" s="121" t="s">
         <v>1039</v>
@@ -43455,7 +43453,7 @@
         <v>24</v>
       </c>
       <c r="F41" s="74" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G41" s="74" t="s">
         <v>111</v>
@@ -43486,7 +43484,7 @@
         <v>108</v>
       </c>
       <c r="P41" s="74" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="Q41" s="74" t="str">
         <f t="shared" si="1"/>
@@ -43508,7 +43506,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="82" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G42" s="82" t="s">
         <v>111</v>
@@ -43533,13 +43531,13 @@
         <v>338</v>
       </c>
       <c r="N42" s="82" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="O42" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P42" s="82" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="Q42" s="82" t="str">
         <f t="shared" si="1"/>
@@ -45577,7 +45575,7 @@
         <v>1035</v>
       </c>
       <c r="E62" s="74" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F62" s="122" t="str">
         <f t="shared" ref="F62:F65" si="14">SUBSTITUTE(E62, "hazr-", "")&amp;"-pb"&amp;H62</f>
@@ -45609,7 +45607,7 @@
         <v>1035</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F63" s="122" t="str">
         <f t="shared" si="14"/>
@@ -45641,7 +45639,7 @@
         <v>1035</v>
       </c>
       <c r="E64" s="82" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F64" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45673,7 +45671,7 @@
         <v>1035</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F65" s="118" t="str">
         <f t="shared" si="14"/>
@@ -45700,12 +45698,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45853,15 +45848,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -45885,17 +45891,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>